--- a/product_template.xlsx
+++ b/product_template.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Test-Team\Desktop\TMax协议\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69064CA1-D6D3-40EA-AA26-FB76F043DDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2680" yWindow="1500" windowWidth="28240" windowHeight="17440" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>ProductNumber</t>
   </si>
@@ -57,42 +46,62 @@
     <t>LimitLow</t>
   </si>
   <si>
-    <t>一个菜单的名称</t>
-  </si>
-  <si>
-    <t>Тестовый True Тестовый True</t>
-  </si>
-  <si>
-    <t>西红柿鸡蛋</t>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Mela</t>
+  </si>
+  <si>
+    <t>Apfel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -104,8 +113,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF9CC2E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,103 +127,77 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -235,7 +217,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CEEACA"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -273,7 +255,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -303,12 +285,29 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -338,6 +337,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -489,155 +505,157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.002500000000003" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.8330078125" customWidth="1" style="13"/>
+    <col min="2" max="2" width="13.998046875" customWidth="1" style="5"/>
+    <col min="3" max="3" width="9.6650390625" customWidth="1" style="12"/>
+    <col min="4" max="4" width="10.3330078125" customWidth="1" style="12"/>
+    <col min="5" max="5" width="9" customWidth="1" style="12"/>
+    <col min="6" max="6" width="6.9990234375" customWidth="1" style="6"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1" style="12"/>
+    <col min="8" max="8" width="8.4990234375" customWidth="1" style="12"/>
+    <col min="9" max="9" width="10.5" customWidth="1" style="12"/>
+    <col min="10" max="10" width="9.3310546875" customWidth="1" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="14.002500000000003" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="C2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.002500000000003" customHeight="1">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.5</v>
+      <c r="B3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>22.22</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" ht="14.002500000000003" customHeight="1">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>33.33</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.5</v>
+      <c r="C4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{ECDA90DA-B366-4D81-BE4E-86AE0F6D61AB}">
-      <formula1>0</formula1>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F3 F4 F5 F6:F1048576">
       <formula2>10000000</formula2>
     </dataValidation>
   </dataValidations>
